--- a/data/trans_orig/IP07C17-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP07C17-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2007 (tasa de respuesta: 89,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4408</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3192</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10529</t>
+          <t>10422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>10114</t>
+          <t>10248</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21430</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>29,24%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15774</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25943</t>
+          <t>25736</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>39,51%</t>
+          <t>39,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,98%</t>
+          <t>64,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10855</t>
+          <t>10452</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19880</t>
+          <t>20093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29191</t>
+          <t>29258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42642</t>
+          <t>43594</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3760</t>
+          <t>3800</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11859</t>
+          <t>11995</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5331</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13860</t>
+          <t>13702</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11070</t>
+          <t>11590</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23219</t>
+          <t>23377</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3804</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2118</t>
+          <t>1571</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2192</t>
+          <t>2263</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10075</t>
+          <t>10747</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>696</t>
+          <t>697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>5976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>708</t>
+          <t>711</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4174</t>
+          <t>4610</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11860</t>
+          <t>11863</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7316</t>
+          <t>7773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15991</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>54,71%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>13908</t>
+          <t>14327</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25003</t>
+          <t>25873</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5768</t>
+          <t>5949</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>13554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,75%</t>
+          <t>53,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6201</t>
+          <t>6187</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14571</t>
+          <t>14215</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14469</t>
+          <t>13988</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25470</t>
+          <t>25157</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,6%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3403</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10939</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,65%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1319</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>7559</t>
+          <t>7040</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6521</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15816</t>
+          <t>16262</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>29,3%</t>
+          <t>30,12%</t>
         </is>
       </c>
     </row>
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>630</t>
+          <t>624</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5283</t>
+          <t>5281</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,7 +1803,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>612</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>5312</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>2960</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3809</t>
+          <t>4499</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1936,12 +1936,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>616</t>
+          <t>621</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>5367</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1951,12 +1951,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4387</t>
+          <t>4343</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12252</t>
+          <t>12884</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>44,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4558</t>
+          <t>4591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12800</t>
+          <t>13369</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10838</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>22399</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>7332</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16246</t>
+          <t>16265</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16022</t>
+          <t>16000</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>27275</t>
+          <t>28052</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27008</t>
+          <t>27021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41756</t>
+          <t>40799</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>50,92%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t>3375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10600</t>
+          <t>11420</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>11429</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21837</t>
+          <t>22130</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,67%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>16437</t>
+          <t>16159</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>29172</t>
+          <t>28949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,13%</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3890</t>
+          <t>4461</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3365</t>
+          <t>3862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,82%</t>
         </is>
       </c>
     </row>
@@ -2548,12 +2548,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>655</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>5628</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2563,12 +2563,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8547</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2598,12 +2598,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2618,12 +2618,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>3822</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>11990</t>
+          <t>12136</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2633,12 +2633,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>17190</t>
+          <t>17213</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>30603</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13773</t>
+          <t>13924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>26595</t>
+          <t>26040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>34200</t>
+          <t>33760</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53677</t>
+          <t>51611</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35614</t>
+          <t>35353</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50797</t>
+          <t>50454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,48%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>58,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22140</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>35812</t>
+          <t>35734</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>61311</t>
+          <t>61867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>82711</t>
+          <t>82943</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,54%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>7545</t>
+          <t>8296</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>18190</t>
+          <t>18884</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,82 +3019,82 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
+          <t>22,0%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>22962</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>17220</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>30357</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>28,15%</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>37,22%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>35477</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>27310</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>44512</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
           <t>21,19%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>22962</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>16524</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>29562</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>28,15%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>20,26%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>36,24%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>35477</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>27132</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>44170</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>21,19%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,0%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>6672</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4868</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>13804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>597</t>
+          <t>591</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,12 +3245,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3265,12 +3265,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4327</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>12513</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>5536</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>15236</t>
+          <t>14977</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>10459</t>
+          <t>10396</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>20489</t>
+          <t>20608</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>7447</t>
+          <t>7439</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17381</t>
+          <t>16888</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20369</t>
+          <t>20479</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>34607</t>
+          <t>35388</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,52%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>14309</t>
+          <t>14129</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>24726</t>
+          <t>25461</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>12636</t>
+          <t>13071</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>24051</t>
+          <t>24075</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>29984</t>
+          <t>29892</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>45228</t>
+          <t>46034</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5692</t>
+          <t>5405</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>14518</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>20267</t>
+          <t>20123</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>33011</t>
+          <t>32441</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>51,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>28174</t>
+          <t>27957</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>44754</t>
+          <t>44203</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>39,97%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>643</t>
+          <t>531</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1386</t>
+          <t>1495</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8107</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3169</t>
+          <t>3245</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>11135</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>10,07%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4440</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3947,12 +3947,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1253</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>7274</t>
+          <t>7696</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2046</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9473</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,57%</t>
         </is>
       </c>
     </row>
@@ -4142,12 +4142,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6386</t>
+          <t>5787</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>14695</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4177,12 +4177,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3184</t>
+          <t>2650</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>9658</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>10578</t>
+          <t>10800</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>21400</t>
+          <t>22700</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>30,7%</t>
+          <t>32,56%</t>
         </is>
       </c>
     </row>
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13004</t>
+          <t>12764</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>22381</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>33,79%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4290,12 +4290,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>9950</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>19000</t>
+          <t>19527</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4325,12 +4325,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>25255</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>38071</t>
+          <t>38666</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>55,47%</t>
         </is>
       </c>
     </row>
@@ -4368,12 +4368,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4383,12 +4383,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4403,12 +4403,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5105</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13592</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4438,12 +4438,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>10641</t>
+          <t>10193</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>21800</t>
+          <t>20945</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -4481,12 +4481,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>6647</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4496,12 +4496,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5069</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4536,7 +4536,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4551,12 +4551,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2062</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>9144</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4566,12 +4566,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,12%</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3269</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3810</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4649,7 +4649,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4664,12 +4664,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>580</t>
+          <t>577</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>5381</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,72%</t>
         </is>
       </c>
     </row>
@@ -4824,12 +4824,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>61671</t>
+          <t>60360</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>84496</t>
+          <t>85073</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,71%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4859,12 +4859,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>52519</t>
+          <t>51344</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>75085</t>
+          <t>74631</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4894,12 +4894,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>119004</t>
+          <t>119793</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>151923</t>
+          <t>152468</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,51%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -4937,12 +4937,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>107212</t>
+          <t>108239</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>135077</t>
+          <t>136378</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4952,12 +4952,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>40,34%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>51,32%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4972,12 +4972,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>94966</t>
+          <t>94339</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>121977</t>
+          <t>121695</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4987,12 +4987,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,41%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>41,9%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5007,12 +5007,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>210383</t>
+          <t>211414</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>247997</t>
+          <t>249248</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5022,12 +5022,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,76%</t>
         </is>
       </c>
     </row>
@@ -5050,12 +5050,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>39588</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>59883</t>
+          <t>60156</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5065,12 +5065,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>22,53%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5085,12 +5085,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>74555</t>
+          <t>75299</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>98754</t>
+          <t>99532</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>121588</t>
+          <t>118516</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>153536</t>
+          <t>151344</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,18%</t>
         </is>
       </c>
     </row>
@@ -5163,12 +5163,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7418</t>
+          <t>7303</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>17893</t>
+          <t>17814</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5178,12 +5178,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5198,12 +5198,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>21873</t>
+          <t>23060</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>19931</t>
+          <t>19828</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>36660</t>
+          <t>36841</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,62%</t>
         </is>
       </c>
     </row>
@@ -5276,12 +5276,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5311,12 +5311,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>12003</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>25255</t>
+          <t>25100</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5326,12 +5326,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>19945</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>36673</t>
+          <t>35882</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5361,12 +5361,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -5545,7 +5545,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2012 (tasa de respuesta: 95,2%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5740,12 +5740,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9163</t>
+          <t>9390</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>18977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5755,12 +5755,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3145</t>
+          <t>2928</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10006</t>
+          <t>10143</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5810,12 +5810,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14037</t>
+          <t>13393</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25843</t>
+          <t>25663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,0%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -5853,12 +5853,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14661</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5868,12 +5868,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5888,12 +5888,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>10352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19631</t>
+          <t>19952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5923,12 +5923,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18552</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31360</t>
+          <t>31793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>25,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>45,52%</t>
         </is>
       </c>
     </row>
@@ -5966,12 +5966,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6627</t>
+          <t>6439</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15600</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5981,12 +5981,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6001,12 +6001,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>6136</t>
+          <t>6010</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14711</t>
+          <t>14858</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>17,91%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>43,85%</t>
+          <t>44,29%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6036,12 +6036,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>14758</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27258</t>
+          <t>27607</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>20,59%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>39,02%</t>
+          <t>39,52%</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4097</t>
+          <t>3907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6099,7 +6099,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6119,7 +6119,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4942</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6134,7 +6134,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1176</t>
+          <t>1187</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>7008</t>
+          <t>7144</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3322</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>642</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5024</t>
+          <t>5661</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,1%</t>
         </is>
       </c>
     </row>
@@ -6422,12 +6422,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7321</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>16250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6437,12 +6437,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,45%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7595</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17183</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29294</t>
+          <t>29030</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -6535,12 +6535,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11001</t>
+          <t>11034</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20115</t>
+          <t>20124</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6550,12 +6550,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19462</t>
+          <t>19805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23739</t>
+          <t>24172</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>37094</t>
+          <t>36887</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -6648,12 +6648,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1574</t>
+          <t>1871</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>8672</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1867</t>
+          <t>1737</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8097</t>
+          <t>7787</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6698,12 +6698,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>5108</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14049</t>
+          <t>13782</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6733,12 +6733,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4432</t>
+          <t>4458</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>848</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7394</t>
+          <t>7643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1850</t>
+          <t>1804</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9331</t>
+          <t>9386</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6846,12 +6846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,86%</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4149</t>
+          <t>4729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6929,7 +6929,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6949,7 +6949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4711</t>
+          <t>4067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -7104,12 +7104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22769</t>
+          <t>21694</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,88%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>50,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5434</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13545</t>
+          <t>13602</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7154,12 +7154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>19807</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>32902</t>
+          <t>32619</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7189,12 +7189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>43,86%</t>
         </is>
       </c>
     </row>
@@ -7217,12 +7217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13355</t>
+          <t>13556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23860</t>
+          <t>24161</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,51%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>7598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16919</t>
+          <t>16226</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7267,12 +7267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24119</t>
+          <t>23779</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37811</t>
+          <t>37807</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1431</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10341</t>
+          <t>9987</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7380,12 +7380,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>31,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>5677</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15828</t>
+          <t>15861</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7415,12 +7415,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -7443,12 +7443,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5449</t>
+          <t>5437</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7493,12 +7493,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7513,12 +7513,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8817</t>
+          <t>7940</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7528,12 +7528,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>10,68%</t>
         </is>
       </c>
     </row>
@@ -7561,7 +7561,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5053</t>
+          <t>5414</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7591,12 +7591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>613</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>6155</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7606,12 +7606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7626,12 +7626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1713</t>
+          <t>1531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>8423</t>
+          <t>7890</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7641,12 +7641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,61%</t>
         </is>
       </c>
     </row>
@@ -7786,12 +7786,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>27783</t>
+          <t>27539</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42795</t>
+          <t>42546</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30417</t>
+          <t>30196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45966</t>
+          <t>46365</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62578</t>
+          <t>62659</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84613</t>
+          <t>84710</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7871,12 +7871,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -7899,12 +7899,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>24046</t>
+          <t>24240</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38525</t>
+          <t>38604</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -7934,12 +7934,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>22698</t>
+          <t>22441</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>37630</t>
+          <t>37291</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7949,12 +7949,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -7969,12 +7969,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51250</t>
+          <t>51279</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71306</t>
+          <t>72105</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7984,12 +7984,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,37%</t>
+          <t>39,81%</t>
         </is>
       </c>
     </row>
@@ -8012,12 +8012,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>7449</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>18205</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8027,12 +8027,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8047,12 +8047,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>25884</t>
+          <t>25596</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8082,12 +8082,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>22040</t>
+          <t>22450</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38808</t>
+          <t>38836</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,43%</t>
+          <t>21,44%</t>
         </is>
       </c>
     </row>
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1435</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>7667</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -8160,12 +8160,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3227</t>
+          <t>3132</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11936</t>
+          <t>11041</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -8175,12 +8175,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -8195,12 +8195,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16783</t>
+          <t>15669</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -8238,12 +8238,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>688</t>
+          <t>686</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6958</t>
+          <t>6814</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -8273,12 +8273,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7536</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -8288,12 +8288,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -8308,12 +8308,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>3006</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>11238</t>
+          <t>11225</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -8323,12 +8323,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -8468,12 +8468,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>20216</t>
+          <t>20596</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>33972</t>
+          <t>34890</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -8483,12 +8483,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -8503,12 +8503,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>18435</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>32715</t>
+          <t>31234</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>25,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -8538,12 +8538,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>42738</t>
+          <t>42803</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>61656</t>
+          <t>62121</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>42,52%</t>
         </is>
       </c>
     </row>
@@ -8581,12 +8581,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>21693</t>
+          <t>20631</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35078</t>
+          <t>35243</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -8596,12 +8596,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,95%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -8616,12 +8616,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>14847</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>28290</t>
+          <t>28434</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -8631,12 +8631,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -8651,12 +8651,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>41453</t>
+          <t>41248</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>60755</t>
+          <t>59721</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -8666,12 +8666,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,59%</t>
+          <t>40,88%</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>9258</t>
+          <t>9555</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>21601</t>
+          <t>21325</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -8709,12 +8709,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>28,91%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -8729,12 +8729,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10176</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21543</t>
+          <t>21857</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -8744,12 +8744,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>22799</t>
+          <t>22521</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>38937</t>
+          <t>40330</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -8779,12 +8779,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>26,65%</t>
+          <t>27,61%</t>
         </is>
       </c>
     </row>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4281</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8827,7 +8827,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8842,12 +8842,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2089</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8857,12 +8857,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>2534</t>
+          <t>2765</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10682</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8892,12 +8892,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -8920,12 +8920,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>7443</t>
+          <t>7417</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8935,12 +8935,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,93%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8955,12 +8955,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>2492</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>9291</t>
+          <t>9773</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8970,12 +8970,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8990,12 +8990,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>4547</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>13814</t>
+          <t>14660</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -9005,12 +9005,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>10,04%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>2711</t>
+          <t>2685</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>9237</t>
+          <t>9230</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -9185,12 +9185,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>3469</t>
+          <t>3691</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>11641</t>
+          <t>11790</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -9200,12 +9200,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>7894</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>18315</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -9235,12 +9235,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -9263,12 +9263,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>4883</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>12377</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -9278,12 +9278,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -9298,12 +9298,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>12156</t>
+          <t>11825</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>21841</t>
+          <t>21733</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -9313,12 +9313,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>33,46%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>61,8%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -9333,12 +9333,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19350</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>32608</t>
+          <t>31589</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -9348,12 +9348,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>33,31%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -9376,12 +9376,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3116</t>
+          <t>3154</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>10446</t>
+          <t>10116</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -9391,12 +9391,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>44,45%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4639</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>12666</t>
+          <t>13078</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -9446,12 +9446,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9298</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>20025</t>
+          <t>20378</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -9461,12 +9461,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>34,03%</t>
+          <t>34,63%</t>
         </is>
       </c>
     </row>
@@ -9489,12 +9489,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>741</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>7087</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -9504,12 +9504,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>4128</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -9544,7 +9544,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -9559,12 +9559,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>1685</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>9503</t>
+          <t>9053</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -9574,12 +9574,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>5030</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -9657,7 +9657,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -9677,7 +9677,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5513</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -9692,7 +9692,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -9832,12 +9832,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>96401</t>
+          <t>95282</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>124292</t>
+          <t>122600</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -9847,12 +9847,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,33%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -9867,12 +9867,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>83602</t>
+          <t>83635</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>110249</t>
+          <t>109246</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -9882,12 +9882,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,02%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -9902,12 +9902,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>188460</t>
+          <t>187913</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>228256</t>
+          <t>226760</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -9917,12 +9917,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -9945,12 +9945,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>97200</t>
+          <t>97898</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>124888</t>
+          <t>126936</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>33,22%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>43,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -9980,12 +9980,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>97448</t>
+          <t>97243</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>124158</t>
+          <t>124404</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>32,13%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -10015,12 +10015,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>203145</t>
+          <t>203368</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>241280</t>
+          <t>241552</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -10030,12 +10030,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -10058,12 +10058,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>41012</t>
+          <t>41561</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>62788</t>
+          <t>62614</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -10073,12 +10073,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,31%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -10093,12 +10093,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>50365</t>
+          <t>51364</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>73482</t>
+          <t>74742</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>99666</t>
+          <t>96892</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>130712</t>
+          <t>128117</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>21,43%</t>
         </is>
       </c>
     </row>
@@ -10171,12 +10171,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7742</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>19459</t>
+          <t>19050</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -10206,12 +10206,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>13528</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>26773</t>
+          <t>26755</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>23101</t>
+          <t>23813</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>42346</t>
+          <t>42481</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,1%</t>
         </is>
       </c>
     </row>
@@ -10284,12 +10284,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>5061</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>15067</t>
+          <t>14086</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>9681</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>21864</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>17295</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>32274</t>
+          <t>32353</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -10553,7 +10553,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
+          <t>Menores según la frecuencia de gustarle ir al colegio en 2016 (tasa de respuesta: 95,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10748,12 +10748,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9100</t>
+          <t>9253</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18254</t>
+          <t>18555</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10763,12 +10763,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,98%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10783,12 +10783,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>9369</t>
+          <t>9572</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>19046</t>
+          <t>19605</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10798,12 +10798,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10818,12 +10818,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34764</t>
+          <t>34303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10833,12 +10833,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>48,97%</t>
         </is>
       </c>
     </row>
@@ -10861,12 +10861,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6316</t>
+          <t>5848</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15328</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10876,12 +10876,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10896,12 +10896,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12128</t>
+          <t>11901</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>21931</t>
+          <t>22144</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10911,12 +10911,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>59,01%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10931,12 +10931,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21079</t>
+          <t>20148</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33942</t>
+          <t>34126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10946,12 +10946,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4766</t>
+          <t>4582</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13197</t>
+          <t>12665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>38,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7954</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>7340</t>
+          <t>7362</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>17733</t>
+          <t>18170</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,32%</t>
+          <t>25,94%</t>
         </is>
       </c>
     </row>
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>596</t>
+          <t>584</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>6091</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>590</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>5444</t>
+          <t>5989</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -11205,7 +11205,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4304</t>
+          <t>4570</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11220,7 +11220,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>2936</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11275,7 +11275,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4945</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11290,7 +11290,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>
@@ -11430,12 +11430,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>10056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21081</t>
+          <t>20801</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11445,12 +11445,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11465,12 +11465,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9763</t>
+          <t>9641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19971</t>
+          <t>20156</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11480,12 +11480,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,45%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11500,12 +11500,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22588</t>
+          <t>21984</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>37835</t>
+          <t>36664</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11515,12 +11515,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -11543,12 +11543,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>15382</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>27087</t>
+          <t>27372</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11558,12 +11558,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,23%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11578,12 +11578,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>12770</t>
+          <t>13021</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>24158</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11593,12 +11593,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11613,12 +11613,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>31228</t>
+          <t>31782</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47776</t>
+          <t>47834</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11628,12 +11628,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,2%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,26%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3255</t>
+          <t>2981</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12262</t>
+          <t>11231</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6983</t>
+          <t>6752</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16928</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>11785</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>25031</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1954</t>
+          <t>1883</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8510</t>
+          <t>8354</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>589</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6736</t>
+          <t>6409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3532</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11793</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>631</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>5641</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4658</t>
+          <t>4447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11937,7 +11937,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1331</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>8529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -12112,12 +12112,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4600</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12571</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12127,12 +12127,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12147,12 +12147,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>5576</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14034</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12162,12 +12162,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12182,12 +12182,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>12009</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>24089</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12197,12 +12197,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,2%</t>
         </is>
       </c>
     </row>
@@ -12225,12 +12225,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9054</t>
+          <t>8671</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17667</t>
+          <t>17572</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12240,12 +12240,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12260,12 +12260,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12266</t>
+          <t>12220</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22595</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12295,12 +12295,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23372</t>
+          <t>23901</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37044</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12310,12 +12310,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>34,65%</t>
+          <t>35,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -12343,7 +12343,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12373,12 +12373,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6599</t>
+          <t>6794</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16256</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12408,12 +12408,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>8015</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>18012</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,46%</t>
+          <t>26,7%</t>
         </is>
       </c>
     </row>
@@ -12451,12 +12451,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8132</t>
+          <t>8229</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12466,12 +12466,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12491,7 +12491,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4526</t>
+          <t>4678</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12506,7 +12506,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12521,12 +12521,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10679</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,13%</t>
         </is>
       </c>
     </row>
@@ -12569,7 +12569,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>3343</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12584,7 +12584,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12634,12 +12634,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>635</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5315</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,88%</t>
         </is>
       </c>
     </row>
@@ -12794,12 +12794,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35068</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>51653</t>
+          <t>51433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12809,12 +12809,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12829,12 +12829,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>25573</t>
+          <t>25015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40958</t>
+          <t>41875</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12844,12 +12844,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12864,12 +12864,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63895</t>
+          <t>63403</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>87968</t>
+          <t>87256</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12879,12 +12879,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,8%</t>
         </is>
       </c>
     </row>
@@ -12907,12 +12907,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>30640</t>
+          <t>30748</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47077</t>
+          <t>47364</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12922,12 +12922,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12942,12 +12942,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>31205</t>
+          <t>31375</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>48328</t>
+          <t>48182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12957,12 +12957,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>66035</t>
+          <t>67014</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>89318</t>
+          <t>91397</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12992,12 +12992,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>32,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,78%</t>
         </is>
       </c>
     </row>
@@ -13020,12 +13020,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>13041</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>25949</t>
+          <t>26251</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13035,12 +13035,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13055,12 +13055,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11415</t>
+          <t>11659</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23719</t>
+          <t>24160</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13070,12 +13070,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -13090,12 +13090,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>27442</t>
+          <t>26925</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>45456</t>
+          <t>45555</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13105,12 +13105,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,82%</t>
         </is>
       </c>
     </row>
@@ -13133,12 +13133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3076</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12148</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13148,12 +13148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13173,7 +13173,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13203,12 +13203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6573</t>
+          <t>7052</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18031</t>
+          <t>17765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13218,12 +13218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -13246,12 +13246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2097</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13261,12 +13261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13281,12 +13281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>755</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13316,12 +13316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4578</t>
+          <t>4265</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14094</t>
+          <t>13840</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13331,12 +13331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -13476,12 +13476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>17195</t>
+          <t>17000</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>30439</t>
+          <t>30121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13491,12 +13491,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>40,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13511,12 +13511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15354</t>
+          <t>15479</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27981</t>
+          <t>28914</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,02%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13546,12 +13546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>35657</t>
+          <t>36109</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>55183</t>
+          <t>54337</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13561,12 +13561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,66%</t>
         </is>
       </c>
     </row>
@@ -13589,12 +13589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>25665</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>39677</t>
+          <t>39213</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13604,12 +13604,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,02%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13624,12 +13624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>19687</t>
+          <t>18855</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>33280</t>
+          <t>32780</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13639,12 +13639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13659,12 +13659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>47772</t>
+          <t>49045</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>68239</t>
+          <t>68503</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13674,12 +13674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,48%</t>
         </is>
       </c>
     </row>
@@ -13702,12 +13702,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8701</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>19237</t>
+          <t>19977</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13717,12 +13717,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>26,01%</t>
+          <t>27,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13737,12 +13737,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>10033</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>21922</t>
+          <t>21696</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13752,12 +13752,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13772,12 +13772,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>20879</t>
+          <t>21305</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>36246</t>
+          <t>37068</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -13787,12 +13787,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,69%</t>
         </is>
       </c>
     </row>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>506</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>4869</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -13830,12 +13830,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -13850,12 +13850,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2373</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10364</t>
+          <t>10463</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -13865,12 +13865,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -13885,12 +13885,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3268</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>12650</t>
+          <t>12111</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -13900,12 +13900,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -13928,12 +13928,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>791</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6621</t>
+          <t>7011</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -13943,12 +13943,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -13963,12 +13963,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>764</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6778</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -13978,12 +13978,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -13998,12 +13998,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10686</t>
+          <t>11124</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14013,12 +14013,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -14158,12 +14158,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>6525</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>15694</t>
+          <t>15727</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -14173,12 +14173,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>47,04%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -14193,12 +14193,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>5669</t>
+          <t>5487</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>14879</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -14208,12 +14208,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -14228,12 +14228,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14365</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>27704</t>
+          <t>27432</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -14243,12 +14243,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>38,9%</t>
         </is>
       </c>
     </row>
@@ -14271,12 +14271,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6488</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>15822</t>
+          <t>16303</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -14286,12 +14286,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>48,87%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -14306,12 +14306,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>13558</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>23332</t>
+          <t>23421</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -14321,12 +14321,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>62,8%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>22106</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>35911</t>
+          <t>35839</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,35%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,82%</t>
         </is>
       </c>
     </row>
@@ -14384,12 +14384,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>6104</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>14533</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -14399,12 +14399,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,56%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -14419,12 +14419,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>3419</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>11009</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -14434,12 +14434,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -14454,12 +14454,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>11056</t>
+          <t>10980</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>22218</t>
+          <t>23450</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -14469,12 +14469,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>33,26%</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>4312</t>
+          <t>3795</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -14517,7 +14517,7 @@
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -14537,7 +14537,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4679</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -14552,7 +14552,7 @@
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -14567,12 +14567,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>735</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>6583</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -14582,12 +14582,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3379</t>
+          <t>3770</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -14650,7 +14650,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4914</t>
+          <t>4219</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -14665,7 +14665,7 @@
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -14685,7 +14685,7 @@
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5622</t>
+          <t>6152</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -14840,12 +14840,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>100656</t>
+          <t>100827</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>128971</t>
+          <t>128765</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -14855,12 +14855,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -14875,12 +14875,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>87085</t>
+          <t>88529</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>115170</t>
+          <t>116803</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -14890,12 +14890,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -14910,12 +14910,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>195678</t>
+          <t>194943</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>237198</t>
+          <t>235705</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -14925,12 +14925,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>36,05%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -14953,12 +14953,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>110693</t>
+          <t>111071</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>141443</t>
+          <t>140037</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -14968,12 +14968,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -14988,12 +14988,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>121344</t>
+          <t>120999</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>152579</t>
+          <t>150338</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -15003,12 +15003,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,56%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -15023,12 +15023,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>242181</t>
+          <t>241123</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>283757</t>
+          <t>283762</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -15038,7 +15038,7 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
@@ -15066,12 +15066,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>47355</t>
+          <t>46980</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>69410</t>
+          <t>69384</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -15081,12 +15081,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -15101,12 +15101,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>52585</t>
+          <t>53311</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>76464</t>
+          <t>76758</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -15116,12 +15116,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -15136,12 +15136,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>105115</t>
+          <t>105110</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>139498</t>
+          <t>139441</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -15179,12 +15179,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>11849</t>
+          <t>11736</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>24751</t>
+          <t>25428</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -15194,12 +15194,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -15214,12 +15214,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>11531</t>
+          <t>11417</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>25336</t>
+          <t>25246</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -15229,12 +15229,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -15249,12 +15249,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>26280</t>
+          <t>26569</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>45759</t>
+          <t>45991</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -15264,12 +15264,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -15292,12 +15292,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>18137</t>
+          <t>19666</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -15307,12 +15307,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -15327,12 +15327,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>6745</t>
+          <t>6267</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>17951</t>
+          <t>17549</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -15342,12 +15342,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -15362,12 +15362,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>15771</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>31408</t>
+          <t>31153</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -15382,7 +15382,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
